--- a/data/trans_orig/P2C_R1-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R1-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2007</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2007 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>816</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7901</t>
+          <t>7243</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2789</t>
+          <t>3148</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16449</t>
+          <t>15569</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4893</t>
+          <t>5011</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18390</t>
+          <t>19201</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>670202</t>
+          <t>670860</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>677285</t>
+          <t>677287</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>983640</t>
+          <t>984520</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>997300</t>
+          <t>996941</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1659802</t>
+          <t>1658991</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1673299</t>
+          <t>1673181</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,7%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>898</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12763</t>
+          <t>13379</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2298</t>
+          <t>2168</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14456</t>
+          <t>13692</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4764</t>
+          <t>4942</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21851</t>
+          <t>20555</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>927445</t>
+          <t>926829</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>939305</t>
+          <t>939310</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>996646</t>
+          <t>997410</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1008804</t>
+          <t>1008934</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1929459</t>
+          <t>1930755</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1946546</t>
+          <t>1946368</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,75%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>878</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9347</t>
+          <t>9406</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,47 +1434,47 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,22%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>4154</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>10439</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
           <t>0,35%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,2%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4154</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1008</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>9582</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3104</t>
+          <t>3120</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14691</t>
+          <t>14603</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>282568</t>
+          <t>282509</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>290883</t>
+          <t>291037</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,49 +1547,49 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>99,7%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>286018</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>279733</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>289165</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>98,57%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>96,4%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
           <t>99,65%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>286018</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>280590</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>289164</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,57%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>96,7%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,65%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>541</t>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>567395</t>
+          <t>567483</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>578982</t>
+          <t>578966</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4736</t>
+          <t>5479</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20677</t>
+          <t>20075</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10664</t>
+          <t>10194</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29730</t>
+          <t>28173</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19490</t>
+          <t>18664</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>44763</t>
+          <t>41428</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1889549</t>
+          <t>1890151</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1905490</t>
+          <t>1904747</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2271632</t>
+          <t>2273189</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2290698</t>
+          <t>2291168</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4166825</t>
+          <t>4170160</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4192098</t>
+          <t>4192924</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,56%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2012</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2012 (tasa de respuesta: 99,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10092</t>
+          <t>10095</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3705</t>
+          <t>3760</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17297</t>
+          <t>17416</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7261</t>
+          <t>6711</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22542</t>
+          <t>22866</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>706906</t>
+          <t>706903</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>715991</t>
+          <t>715987</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1045014</t>
+          <t>1044895</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1058606</t>
+          <t>1058551</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1756767</t>
+          <t>1756443</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1772048</t>
+          <t>1772598</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8152</t>
+          <t>7907</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4984</t>
+          <t>4906</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18368</t>
+          <t>18883</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7023</t>
+          <t>6899</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22519</t>
+          <t>22666</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1150019</t>
+          <t>1150264</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1157236</t>
+          <t>1158171</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1164517</t>
+          <t>1164002</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1177901</t>
+          <t>1177979</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2318537</t>
+          <t>2318390</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2334033</t>
+          <t>2334157</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,71%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4636</t>
+          <t>4733</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20027</t>
+          <t>18566</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>4685</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18682</t>
+          <t>20996</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11292</t>
+          <t>10813</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32257</t>
+          <t>30951</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>239551</t>
+          <t>241012</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>254942</t>
+          <t>254845</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>249842</t>
+          <t>247528</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>263801</t>
+          <t>263839</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>495844</t>
+          <t>497150</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>516809</t>
+          <t>517288</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,95%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9019</t>
+          <t>9658</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27773</t>
+          <t>28298</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19089</t>
+          <t>19350</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42836</t>
+          <t>44015</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32516</t>
+          <t>32950</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60428</t>
+          <t>61594</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2106973</t>
+          <t>2106448</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2125727</t>
+          <t>2125088</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2470884</t>
+          <t>2469705</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2494631</t>
+          <t>2494370</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4588038</t>
+          <t>4586872</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4615950</t>
+          <t>4615516</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2016</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2016 (tasa de respuesta: 94,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>804</t>
+          <t>802</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8393</t>
+          <t>7274</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,47 +3954,47 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>4865</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1275</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>11925</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
           <t>0,16%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4865</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1343</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>12361</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3215</t>
+          <t>3369</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15533</t>
+          <t>15884</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>509857</t>
+          <t>510976</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>517446</t>
+          <t>517448</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,49 +4067,49 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>99,85%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>690</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>780694</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>773634</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>784284</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>99,38%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>98,48%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
           <t>99,84%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>690</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>780694</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>773198</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>784216</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,38%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>98,43%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>99,83%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>1226</t>
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1288277</t>
+          <t>1287926</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1300595</t>
+          <t>1300441</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>6271</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21211</t>
+          <t>21068</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3039</t>
+          <t>3091</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14243</t>
+          <t>14555</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11709</t>
+          <t>11135</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29402</t>
+          <t>28915</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1080731</t>
+          <t>1080874</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1096064</t>
+          <t>1095671</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1218302</t>
+          <t>1217990</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1229506</t>
+          <t>1229454</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2305085</t>
+          <t>2305572</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2322778</t>
+          <t>2323352</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>985</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8449</t>
+          <t>8575</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5755</t>
+          <t>4951</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18727</t>
+          <t>18810</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7734</t>
+          <t>7639</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22578</t>
+          <t>23198</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>259880</t>
+          <t>259754</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>267355</t>
+          <t>267344</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>293693</t>
+          <t>293610</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>306665</t>
+          <t>307469</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>558171</t>
+          <t>557551</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>573015</t>
+          <t>573110</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10542</t>
+          <t>10456</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27189</t>
+          <t>27795</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13679</t>
+          <t>13741</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33539</t>
+          <t>34225</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28689</t>
+          <t>29201</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54952</t>
+          <t>55021</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,7 +5053,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1861332</t>
+          <t>1860726</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1877979</t>
+          <t>1878065</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2296985</t>
+          <t>2296299</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2316845</t>
+          <t>2316783</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4164093</t>
+          <t>4164024</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4190356</t>
+          <t>4189844</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2023</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2023 (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28160</t>
+          <t>28049</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45164</t>
+          <t>44509</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>72896</t>
+          <t>72562</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>94199</t>
+          <t>95842</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>106919</t>
+          <t>105492</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>133794</t>
+          <t>132601</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>36,41%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69249</t>
+          <t>69904</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>86253</t>
+          <t>86364</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>61,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>155619</t>
+          <t>153976</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>176922</t>
+          <t>177256</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>230437</t>
+          <t>231630</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>257312</t>
+          <t>258739</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>71,04%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24490</t>
+          <t>24336</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44897</t>
+          <t>46415</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9563</t>
+          <t>9769</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45045</t>
+          <t>45557</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24154</t>
+          <t>28843</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>84277</t>
+          <t>84379</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,93%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>248797</t>
+          <t>247279</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>269204</t>
+          <t>269358</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>511192</t>
+          <t>510680</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>546674</t>
+          <t>546468</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>765654</t>
+          <t>765552</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>825777</t>
+          <t>821088</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>96,61%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5267</t>
+          <t>5069</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23037</t>
+          <t>23329</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6490</t>
+          <t>6268</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15440</t>
+          <t>15525</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14919</t>
+          <t>14385</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34115</t>
+          <t>34213</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,14%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>57407</t>
+          <t>57115</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>75177</t>
+          <t>75375</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>73996</t>
+          <t>73911</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>82946</t>
+          <t>83168</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>135764</t>
+          <t>135666</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>154960</t>
+          <t>155494</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,53%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66110</t>
+          <t>66874</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>99430</t>
+          <t>98891</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62907</t>
+          <t>63193</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>161127</t>
+          <t>161664</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>120186</t>
+          <t>122196</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>243054</t>
+          <t>241155</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,42%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>389121</t>
+          <t>389660</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>422441</t>
+          <t>421677</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>79,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>734364</t>
+          <t>733827</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>832584</t>
+          <t>832298</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1140988</t>
+          <t>1142887</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1263856</t>
+          <t>1261846</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,17%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2C_R1-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R1-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>820</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7243</t>
+          <t>7278</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3148</t>
+          <t>2923</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15569</t>
+          <t>14739</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5011</t>
+          <t>4987</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19201</t>
+          <t>19285</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>670860</t>
+          <t>670825</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>677287</t>
+          <t>677283</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>984520</t>
+          <t>985350</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>996941</t>
+          <t>997166</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1658991</t>
+          <t>1658907</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1673181</t>
+          <t>1673205</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>901</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13379</t>
+          <t>14039</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,44 +1096,44 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>6225</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2197</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>14314</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
           <t>1,42%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>6225</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2168</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>13692</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>8</t>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4942</t>
+          <t>4560</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20555</t>
+          <t>22211</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>926829</t>
+          <t>926169</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>939310</t>
+          <t>939307</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,47 +1204,47 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>98,51%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,9%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1004877</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>996788</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>1008905</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>99,38%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
           <t>98,58%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,9%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1004877</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>997410</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1008934</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,38%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,65%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1930755</t>
+          <t>1929099</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1946368</t>
+          <t>1946750</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,77%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>861</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9406</t>
+          <t>8771</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>995</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10439</t>
+          <t>9591</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3120</t>
+          <t>3691</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14603</t>
+          <t>14723</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>282509</t>
+          <t>283144</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>291037</t>
+          <t>291054</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>279733</t>
+          <t>280581</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>289165</t>
+          <t>289177</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>567483</t>
+          <t>567363</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>578966</t>
+          <t>578395</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5479</t>
+          <t>6058</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20075</t>
+          <t>20774</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10194</t>
+          <t>10648</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28173</t>
+          <t>29809</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,47 +1812,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>28781</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>18714</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>41885</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>0,44%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>28781</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>18664</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>41428</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1890151</t>
+          <t>1889452</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1904747</t>
+          <t>1904168</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2273189</t>
+          <t>2271553</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2291168</t>
+          <t>2290714</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4170160</t>
+          <t>4169703</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4192924</t>
+          <t>4192874</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>995</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10095</t>
+          <t>9214</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3760</t>
+          <t>4165</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17416</t>
+          <t>17290</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6711</t>
+          <t>6753</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22866</t>
+          <t>21770</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>706903</t>
+          <t>707784</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>715987</t>
+          <t>716003</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1044895</t>
+          <t>1045021</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1058551</t>
+          <t>1058146</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1756443</t>
+          <t>1757539</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1772598</t>
+          <t>1772556</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>938</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7907</t>
+          <t>8398</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4906</t>
+          <t>4940</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18883</t>
+          <t>19009</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6899</t>
+          <t>7093</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22666</t>
+          <t>22216</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1150264</t>
+          <t>1149773</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1158171</t>
+          <t>1157233</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1164002</t>
+          <t>1163876</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1177979</t>
+          <t>1177945</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2318390</t>
+          <t>2318840</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2334157</t>
+          <t>2333963</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,7%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4733</t>
+          <t>4671</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18566</t>
+          <t>19213</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4685</t>
+          <t>4115</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20996</t>
+          <t>18645</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10813</t>
+          <t>11307</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30951</t>
+          <t>30847</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>241012</t>
+          <t>240365</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>254845</t>
+          <t>254907</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>247528</t>
+          <t>249879</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>263839</t>
+          <t>264409</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>497150</t>
+          <t>497254</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>517288</t>
+          <t>516794</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,86%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9658</t>
+          <t>9462</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28298</t>
+          <t>28409</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19350</t>
+          <t>18801</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44015</t>
+          <t>43121</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32950</t>
+          <t>32580</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>61594</t>
+          <t>62686</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2106448</t>
+          <t>2106337</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2125088</t>
+          <t>2125284</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2469705</t>
+          <t>2470599</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2494370</t>
+          <t>2494919</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4586872</t>
+          <t>4585780</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4615516</t>
+          <t>4615886</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>804</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7274</t>
+          <t>7483</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11925</t>
+          <t>11440</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3369</t>
+          <t>3556</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15884</t>
+          <t>15252</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>510976</t>
+          <t>510767</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>517448</t>
+          <t>517446</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>773634</t>
+          <t>774119</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>784284</t>
+          <t>784291</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1287926</t>
+          <t>1288558</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1300441</t>
+          <t>1300254</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,73%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>5988</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21068</t>
+          <t>20682</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3091</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14555</t>
+          <t>14527</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11135</t>
+          <t>11369</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28915</t>
+          <t>29907</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1080874</t>
+          <t>1081260</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1095671</t>
+          <t>1095954</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1217990</t>
+          <t>1218018</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1229454</t>
+          <t>1229464</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2305572</t>
+          <t>2304580</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2323352</t>
+          <t>2323118</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>989</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8575</t>
+          <t>9057</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4951</t>
+          <t>4981</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18810</t>
+          <t>18466</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7639</t>
+          <t>7756</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23198</t>
+          <t>22508</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>259754</t>
+          <t>259272</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>267344</t>
+          <t>267340</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>293610</t>
+          <t>293954</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>307469</t>
+          <t>307439</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>557551</t>
+          <t>558241</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>573110</t>
+          <t>572993</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,66%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10456</t>
+          <t>10212</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27795</t>
+          <t>27810</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13741</t>
+          <t>14176</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34225</t>
+          <t>33860</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29201</t>
+          <t>29090</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>55021</t>
+          <t>54360</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1860726</t>
+          <t>1860711</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1878065</t>
+          <t>1878309</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2296299</t>
+          <t>2296664</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2316783</t>
+          <t>2316348</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4164024</t>
+          <t>4164685</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4189844</t>
+          <t>4189955</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>36069</t>
+          <t>38387</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28049</t>
+          <t>30198</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44509</t>
+          <t>48205</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>83232</t>
+          <t>88886</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>72562</t>
+          <t>77216</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>95842</t>
+          <t>101652</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>119301</t>
+          <t>127273</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>105492</t>
+          <t>113378</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>132601</t>
+          <t>143207</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>35,6%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>78344</t>
+          <t>86992</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69904</t>
+          <t>77174</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>86364</t>
+          <t>95181</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>69,38%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>61,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>166586</t>
+          <t>187956</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>153976</t>
+          <t>175190</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>177256</t>
+          <t>199626</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>244930</t>
+          <t>274948</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>231630</t>
+          <t>259014</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>258739</t>
+          <t>288843</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>64,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>71,81%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>114413</t>
+          <t>125379</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>114413</t>
+          <t>125379</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>114413</t>
+          <t>125379</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>249818</t>
+          <t>276842</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>249818</t>
+          <t>276842</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>249818</t>
+          <t>276842</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>364231</t>
+          <t>402221</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>364231</t>
+          <t>402221</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>364231</t>
+          <t>402221</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>33653</t>
+          <t>34260</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24336</t>
+          <t>25501</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46415</t>
+          <t>46472</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>26005</t>
+          <t>31021</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9769</t>
+          <t>23215</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45557</t>
+          <t>41598</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>59658</t>
+          <t>65281</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28843</t>
+          <t>52871</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>84379</t>
+          <t>81952</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,91%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>260041</t>
+          <t>309423</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>247279</t>
+          <t>297211</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>269358</t>
+          <t>318182</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>530232</t>
+          <t>376641</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>510680</t>
+          <t>366064</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>546468</t>
+          <t>384447</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>790273</t>
+          <t>686064</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>765552</t>
+          <t>669393</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>821088</t>
+          <t>698474</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>92,96%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>293694</t>
+          <t>343683</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>293694</t>
+          <t>343683</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>293694</t>
+          <t>343683</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>556237</t>
+          <t>407662</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>556237</t>
+          <t>407662</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>556237</t>
+          <t>407662</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>849931</t>
+          <t>751345</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>849931</t>
+          <t>751345</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>849931</t>
+          <t>751345</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>11611</t>
+          <t>12181</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5069</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23329</t>
+          <t>25894</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10293</t>
+          <t>10966</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6268</t>
+          <t>6580</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15525</t>
+          <t>17031</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>21904</t>
+          <t>23147</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14385</t>
+          <t>14070</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34213</t>
+          <t>36364</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>18,68%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>68833</t>
+          <t>78713</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>57115</t>
+          <t>65000</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>75375</t>
+          <t>85303</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>71,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>79143</t>
+          <t>92854</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>73911</t>
+          <t>86789</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>83168</t>
+          <t>97240</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>147975</t>
+          <t>171566</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>135666</t>
+          <t>158349</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>155494</t>
+          <t>180643</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>81,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>92,77%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>80444</t>
+          <t>90894</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>80444</t>
+          <t>90894</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>80444</t>
+          <t>90894</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>89436</t>
+          <t>103820</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>89436</t>
+          <t>103820</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>89436</t>
+          <t>103820</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>169879</t>
+          <t>194713</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>169879</t>
+          <t>194713</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>169879</t>
+          <t>194713</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>81334</t>
+          <t>84828</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66874</t>
+          <t>69593</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>98891</t>
+          <t>104492</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>119530</t>
+          <t>130872</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>63193</t>
+          <t>115012</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>161664</t>
+          <t>148386</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>200864</t>
+          <t>215701</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>122196</t>
+          <t>192743</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>241155</t>
+          <t>240402</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,83%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>407217</t>
+          <t>475128</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>389660</t>
+          <t>455464</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>421677</t>
+          <t>490363</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>775961</t>
+          <t>657452</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>733827</t>
+          <t>639938</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>832298</t>
+          <t>673312</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1183178</t>
+          <t>1132579</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1142887</t>
+          <t>1107878</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1261846</t>
+          <t>1155537</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>85,7%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>488551</t>
+          <t>559956</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>488551</t>
+          <t>559956</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>488551</t>
+          <t>559956</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>895491</t>
+          <t>788324</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>895491</t>
+          <t>788324</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>895491</t>
+          <t>788324</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1384042</t>
+          <t>1348280</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1384042</t>
+          <t>1348280</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1384042</t>
+          <t>1348280</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">

--- a/data/trans_orig/P2C_R1-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R1-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2007 (tasa de respuesta: 99,95%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados y estos son remunerados en 2007 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2012 (tasa de respuesta: 99,27%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados y estos son remunerados en 2012 (tasa de respuesta: 99,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2016 (tasa de respuesta: 94,57%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados y estos son remunerados en 2016 (tasa de respuesta: 94,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2023 (tasa de respuesta: 99,88%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados y estos son remunerados en 2023 (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
